--- a/Result/profitability/3176.xlsx
+++ b/Result/profitability/3176.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>59.53625</v>
+        <v>60.43125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>64.29125000000001</v>
+        <v>65.6275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -888,13 +888,13 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>65.3325</v>
+        <v>63.93125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>59.5325</v>
+        <v>60.04625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>63.10125</v>
+        <v>65.42750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>65.34875000000001</v>
+        <v>65.74625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>65.0675</v>
+        <v>65.96124999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9407,6 +9407,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3176</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>285</v>
+      </c>
+      <c r="D72" t="n">
+        <v>114</v>
+      </c>
+      <c r="E72" t="n">
+        <v>171</v>
+      </c>
+      <c r="F72" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>20</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6.94%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-11</v>
+      </c>
+      <c r="J72" t="n">
+        <v>9</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.295</v>
+      </c>
+      <c r="N72" t="n">
+        <v>54.93875</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>7.149999999999999</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.1355450236966824</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.2962962962962963</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.109999999999999</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.07366911632909123</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
